--- a/summer 2026/Spring Creek Bell Field Project/SPC_Calibration.xlsx
+++ b/summer 2026/Spring Creek Bell Field Project/SPC_Calibration.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,17 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HydroResearch\Documents\GitHub\summer_26\summer 2026\Spring Creek Bell Field Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2CEFDF8-9289-415E-A5E6-A4A923A31C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6B1220-93B8-4114-8D44-2639C5B626AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Well_Sampling_Data_P1" sheetId="1" r:id="rId1"/>
     <sheet name=" SPC calibration data clean" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -27,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="2536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="2541">
   <si>
     <t>Well</t>
   </si>
@@ -7635,13 +7645,28 @@
   </si>
   <si>
     <t>*HOBO sampling resumes on the 27th</t>
+  </si>
+  <si>
+    <t>corrected manual SPC</t>
+  </si>
+  <si>
+    <t>HOBO Specific Conductivity</t>
+  </si>
+  <si>
+    <t>Manual SPC bottom before</t>
+  </si>
+  <si>
+    <t>corrected the other way??</t>
+  </si>
+  <si>
+    <t>post 2025????????</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7772,6 +7797,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -8166,7 +8197,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -8183,6 +8214,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -8294,19 +8329,8 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet2!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Manual: SPC bottom before</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="rnd">
               <a:noFill/>
               <a:round/>
             </a:ln>
@@ -8373,7 +8397,1280 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet2!$B$2:$B$24</c:f>
+              <c:f>Sheet2!$B$3:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>808.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>810.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>816.7</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>846.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>854.4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>857.4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>860.3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>738.79705810546898</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>736.90393066406205</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>733.89263916015602</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>734.692138671875</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>734.65979003906205</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>726.88873291015602</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>725.42333984375</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>723.75238037109398</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>726.08782958984398</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>680.23907470703102</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>739.20343017578102</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>740.78375244140602</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>732.68731689453102</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>736.81866455078102</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>740.91064453125</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$C$3:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>796</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>809</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>844</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>845</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>848</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>822</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>821</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>819</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>824</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>848</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>877</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>838</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>872</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>864</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>871</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>868</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>833</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-88E4-41DB-9FC0-C0FAE516616C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1266562288"/>
+        <c:axId val="1266559792"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1266562288"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1266559792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1266559792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1266562288"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.3767279090113735E-2"/>
+                  <c:y val="6.4870953630796147E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet2!$B$10:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>738.79705810546898</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>736.90393066406205</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>733.89263916015602</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>734.692138671875</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>734.65979003906205</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>726.88873291015602</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>725.42333984375</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>723.75238037109398</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>726.08782958984398</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>680.23907470703102</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>739.20343017578102</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>740.78375244140602</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>732.68731689453102</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>736.81866455078102</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>740.91064453125</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$C$10:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>822</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>821</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>819</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>824</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>848</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>877</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>838</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>872</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>864</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>871</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>868</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>833</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1146-4150-AB6C-CFF1358113DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1266503792"/>
+        <c:axId val="1266501712"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1266503792"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1266501712"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1266501712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1266503792"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet2!$B$10:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>738.79705810546898</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>736.90393066406205</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>733.89263916015602</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>734.692138671875</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>734.65979003906205</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>726.88873291015602</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>725.42333984375</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>723.75238037109398</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>726.08782958984398</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>680.23907470703102</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>739.20343017578102</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>740.78375244140602</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>732.68731689453102</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>736.81866455078102</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>740.91064453125</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet2!$C$10:$C$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>822</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>821</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>819</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>824</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>848</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>877</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>838</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>872</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>864</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>871</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>868</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>833</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0C58-4868-8C9D-9D56A1142A24}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1611431728"/>
+        <c:axId val="1611418000"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1611431728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1611418000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1611418000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1611431728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.7136920384951879E-2"/>
+                  <c:y val="0.11936533974919801"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
@@ -8451,75 +9748,78 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet2!$C$2:$C$24</c:f>
+              <c:f>Sheet1!$C$2:$C$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>765</c:v>
+                </c:pt>
                 <c:pt idx="1">
-                  <c:v>796</c:v>
+                  <c:v>772</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>795</c:v>
+                  <c:v>797</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>809</c:v>
+                  <c:v>819</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>853</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>851</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>867</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>865</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>829</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>791</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>827</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>834</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>834</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>834</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>825</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>844</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>845</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>848</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>850</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>822</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>821</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>819</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>820</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>824</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>848</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>850</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>875</c:v>
-                </c:pt>
                 <c:pt idx="16">
-                  <c:v>877</c:v>
+                  <c:v>856</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>838</c:v>
+                  <c:v>839</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>872</c:v>
+                  <c:v>843</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>864</c:v>
+                  <c:v>847</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>871</c:v>
+                  <c:v>835</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>868</c:v>
+                  <c:v>841</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>833</c:v>
+                  <c:v>836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8527,7 +9827,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5639-4EB7-A36D-378792C9D49D}"/>
+              <c16:uniqueId val="{00000000-7B62-4E28-AB92-7A4BCC09EFB6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8539,14 +9839,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1190390527"/>
-        <c:axId val="1190392191"/>
+        <c:axId val="1547218768"/>
+        <c:axId val="1547212944"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1190390527"/>
+        <c:axId val="1547218768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="600"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -8601,12 +9900,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1190392191"/>
+        <c:crossAx val="1547212944"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1190392191"/>
+        <c:axId val="1547212944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8663,7 +9962,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1190390527"/>
+        <c:crossAx val="1547218768"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -8720,6 +10019,126 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -9275,27 +10694,1688 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>166687</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>471487</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFAA0030-D7B8-4E6A-A181-6C495140E264}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>385762</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>138112</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>80962</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91E5E517-E580-4DD0-AE69-77D658EFE1A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4762</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>128587</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>309562</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>14287</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="9" name="Chart 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAC4651C-2C31-4AD0-B93B-D2551A90108B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB2B0948-EB33-4507-A5DE-9B19C4A69AAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>519112</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>214312</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BF4267B-24A2-4A4D-8DC3-3E07D209A40F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9612,7 +12692,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11187,7 +14267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O2505"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31836,25 +34916,36 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>29</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>27</v>
+        <v>2537</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>2534</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>2538</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>2536</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>2540</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>86</v>
       </c>
@@ -31863,7 +34954,7 @@
       </c>
       <c r="C2" s="13"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>181</v>
       </c>
@@ -31873,8 +34964,16 @@
       <c r="C3" s="13">
         <v>796</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <f>(C3-926.25)/(-0.1124)</f>
+        <v>1158.8078291814948</v>
+      </c>
+      <c r="F3">
+        <f>(-0.1124*B3)+926.25</f>
+        <v>835.41956000000005</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>276</v>
       </c>
@@ -31884,8 +34983,16 @@
       <c r="C4" s="13">
         <v>795</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <f t="shared" ref="D4:D24" si="0">(C4-926.25)/(-0.1124)</f>
+        <v>1167.7046263345196</v>
+      </c>
+      <c r="F4">
+        <f t="shared" ref="F4:F24" si="1">(-0.1124*B4)+926.25</f>
+        <v>835.12732000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>375</v>
       </c>
@@ -31895,8 +35002,16 @@
       <c r="C5" s="13">
         <v>809</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>1043.1494661921708</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>834.45291999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>472</v>
       </c>
@@ -31906,8 +35021,16 @@
       <c r="C6" s="13">
         <v>844</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>731.76156583629893</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>831.06968000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>569</v>
       </c>
@@ -31917,8 +35040,16 @@
       <c r="C7" s="13">
         <v>845</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>722.86476868327406</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>830.21543999999994</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>667</v>
       </c>
@@ -31928,8 +35059,16 @@
       <c r="C8" s="13">
         <v>848</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>696.17437722419925</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>829.87824000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>764</v>
       </c>
@@ -31939,8 +35078,16 @@
       <c r="C9" s="13">
         <v>850</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>678.38078291814952</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>829.55228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>821</v>
       </c>
@@ -31950,8 +35097,20 @@
       <c r="C10" s="13">
         <v>822</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>927.49110320284694</v>
+      </c>
+      <c r="E10">
+        <f>(C10-878.38)/(-0.0433)</f>
+        <v>1302.0785219399538</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>843.20921066894527</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>1303</v>
       </c>
@@ -31961,8 +35120,20 @@
       <c r="C11" s="13">
         <v>821</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>936.38790035587192</v>
+      </c>
+      <c r="E11">
+        <f t="shared" ref="E11:E24" si="2">(C11-878.38)/(-0.0433)</f>
+        <v>1325.1732101616628</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>843.4219981933594</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>1400</v>
       </c>
@@ -31972,8 +35143,20 @@
       <c r="C12" s="13">
         <v>819</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>954.18149466192176</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>1371.3625866050809</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>843.7604673583985</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>1496</v>
       </c>
@@ -31983,8 +35166,20 @@
       <c r="C13" s="13">
         <v>820</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>945.28469750889678</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="2"/>
+        <v>1348.2678983833719</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>843.67060361328129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>1591</v>
       </c>
@@ -31994,8 +35189,20 @@
       <c r="C14" s="13">
         <v>824</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>909.6975088967971</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="2"/>
+        <v>1255.8891454965358</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>843.67423959960945</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>1694</v>
       </c>
@@ -32005,8 +35212,20 @@
       <c r="C15" s="13">
         <v>848</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>696.17437722419925</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>701.61662817551951</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>844.54770642089852</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>1788</v>
       </c>
@@ -32016,8 +35235,20 @@
       <c r="C16" s="13">
         <v>850</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>678.38078291814952</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>655.42725173210158</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>844.7124166015625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>1886</v>
       </c>
@@ -32027,8 +35258,20 @@
       <c r="C17" s="13">
         <v>875</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>455.96085409252669</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>78.060046189376337</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>844.90023244628901</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>1977</v>
       </c>
@@ -32038,19 +35281,44 @@
       <c r="C18" s="13">
         <v>877</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>438.16725978647685</v>
+      </c>
+      <c r="E18" s="18">
+        <f t="shared" si="2"/>
+        <v>31.870669745958327</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>844.63772795410159</v>
+      </c>
+      <c r="G18" s="16"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>2073</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="17">
         <v>680.23907470703102</v>
       </c>
       <c r="C19" s="13">
         <v>838</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>785.14234875444845</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="2"/>
+        <v>932.5635103926096</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>849.79112800292967</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>2169</v>
       </c>
@@ -32060,8 +35328,20 @@
       <c r="C20" s="13">
         <v>872</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>482.65124555160145</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="2"/>
+        <v>147.34411085450336</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>843.16353444824222</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>2270</v>
       </c>
@@ -32071,8 +35351,20 @@
       <c r="C21" s="13">
         <v>864</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>553.82562277580075</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="2"/>
+        <v>332.10161662817541</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>842.98590622558595</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>2360</v>
       </c>
@@ -32082,8 +35374,20 @@
       <c r="C22" s="13">
         <v>871</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>491.54804270462631</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="2"/>
+        <v>170.43879907621238</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>843.89594558105478</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>2435</v>
       </c>
@@ -32093,8 +35397,20 @@
       <c r="C23" s="13">
         <v>868</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>518.23843416370107</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="2"/>
+        <v>239.72286374133941</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>843.43158210449224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>2533</v>
       </c>
@@ -32103,6 +35419,390 @@
       </c>
       <c r="C24" s="13">
         <v>833</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>829.62633451957299</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="2"/>
+        <v>1048.0369515011546</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>842.97164355468749</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2895EEA1-A7E6-4514-AA41-BF4C4751538D}">
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>2537</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="13">
+        <v>798.5</v>
+      </c>
+      <c r="C2">
+        <v>765</v>
+      </c>
+      <c r="D2" s="19">
+        <f>(C2-817.45)/(0.0172)</f>
+        <v>-3049.4186046511654</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="13">
+        <v>808.1</v>
+      </c>
+      <c r="C3">
+        <v>772</v>
+      </c>
+      <c r="D3" s="19">
+        <f t="shared" ref="D3:D24" si="0">(C3-817.45)/(0.0172)</f>
+        <v>-2642.4418604651191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" s="13">
+        <v>810.7</v>
+      </c>
+      <c r="C4">
+        <v>797</v>
+      </c>
+      <c r="D4" s="19">
+        <f t="shared" si="0"/>
+        <v>-1188.9534883720958</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="B5" s="13">
+        <v>816.7</v>
+      </c>
+      <c r="C5">
+        <v>819</v>
+      </c>
+      <c r="D5" s="19">
+        <f t="shared" si="0"/>
+        <v>90.116279069764801</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="B6" s="13">
+        <v>846.8</v>
+      </c>
+      <c r="C6">
+        <v>853</v>
+      </c>
+      <c r="D6" s="19">
+        <f t="shared" si="0"/>
+        <v>2066.8604651162764</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="B7" s="13">
+        <v>854.4</v>
+      </c>
+      <c r="C7">
+        <v>851</v>
+      </c>
+      <c r="D7" s="19">
+        <f t="shared" si="0"/>
+        <v>1950.5813953488346</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="B8" s="13">
+        <v>857.4</v>
+      </c>
+      <c r="C8">
+        <v>867</v>
+      </c>
+      <c r="D8" s="19">
+        <f t="shared" si="0"/>
+        <v>2880.8139534883694</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>764</v>
+      </c>
+      <c r="B9" s="13">
+        <v>860.3</v>
+      </c>
+      <c r="C9">
+        <v>865</v>
+      </c>
+      <c r="D9" s="19">
+        <f t="shared" si="0"/>
+        <v>2764.5348837209276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>821</v>
+      </c>
+      <c r="B10" s="13">
+        <v>738.79705810546898</v>
+      </c>
+      <c r="C10">
+        <v>829</v>
+      </c>
+      <c r="D10" s="19">
+        <f t="shared" si="0"/>
+        <v>671.51162790697413</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B11" s="13">
+        <v>736.90393066406205</v>
+      </c>
+      <c r="C11">
+        <v>791</v>
+      </c>
+      <c r="D11" s="19">
+        <f t="shared" si="0"/>
+        <v>-1537.7906976744212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B12" s="13">
+        <v>733.89263916015602</v>
+      </c>
+      <c r="C12">
+        <v>827</v>
+      </c>
+      <c r="D12" s="19">
+        <f t="shared" si="0"/>
+        <v>555.23255813953222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B13" s="13">
+        <v>734.692138671875</v>
+      </c>
+      <c r="C13">
+        <v>834</v>
+      </c>
+      <c r="D13" s="19">
+        <f t="shared" si="0"/>
+        <v>962.20930232557873</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B14" s="13">
+        <v>734.65979003906205</v>
+      </c>
+      <c r="C14">
+        <v>834</v>
+      </c>
+      <c r="D14" s="19">
+        <f t="shared" si="0"/>
+        <v>962.20930232557873</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B15" s="13">
+        <v>726.88873291015602</v>
+      </c>
+      <c r="C15">
+        <v>834</v>
+      </c>
+      <c r="D15" s="19">
+        <f t="shared" si="0"/>
+        <v>962.20930232557873</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B16" s="13">
+        <v>725.42333984375</v>
+      </c>
+      <c r="C16">
+        <v>825</v>
+      </c>
+      <c r="D16" s="19">
+        <f t="shared" si="0"/>
+        <v>438.95348837209036</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B17" s="13">
+        <v>723.75238037109398</v>
+      </c>
+      <c r="C17">
+        <v>844</v>
+      </c>
+      <c r="D17" s="19">
+        <f t="shared" si="0"/>
+        <v>1543.6046511627881</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B18" s="13">
+        <v>726.08782958984398</v>
+      </c>
+      <c r="C18">
+        <v>856</v>
+      </c>
+      <c r="D18" s="19">
+        <f t="shared" si="0"/>
+        <v>2241.2790697674391</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B19" s="17">
+        <v>680.23907470703102</v>
+      </c>
+      <c r="C19">
+        <v>839</v>
+      </c>
+      <c r="D19" s="19">
+        <f t="shared" si="0"/>
+        <v>1252.9069767441833</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B20" s="13">
+        <v>739.20343017578102</v>
+      </c>
+      <c r="C20">
+        <v>843</v>
+      </c>
+      <c r="D20" s="19">
+        <f t="shared" si="0"/>
+        <v>1485.4651162790672</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B21" s="13">
+        <v>740.78375244140602</v>
+      </c>
+      <c r="C21">
+        <v>847</v>
+      </c>
+      <c r="D21" s="19">
+        <f t="shared" si="0"/>
+        <v>1718.0232558139508</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B22" s="13">
+        <v>732.68731689453102</v>
+      </c>
+      <c r="C22">
+        <v>835</v>
+      </c>
+      <c r="D22" s="19">
+        <f t="shared" si="0"/>
+        <v>1020.3488372092996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B23" s="13">
+        <v>736.81866455078102</v>
+      </c>
+      <c r="C23">
+        <v>841</v>
+      </c>
+      <c r="D23" s="19">
+        <f t="shared" si="0"/>
+        <v>1369.1860465116254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B24" s="13">
+        <v>740.91064453125</v>
+      </c>
+      <c r="C24">
+        <v>836</v>
+      </c>
+      <c r="D24" s="19">
+        <f t="shared" si="0"/>
+        <v>1078.4883720930206</v>
       </c>
     </row>
   </sheetData>
